--- a/Documentation/Notes/2026 Summer Calendar Template - huan1811.xlsx
+++ b/Documentation/Notes/2026 Summer Calendar Template - huan1811.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhuang/Desktop/School/Biomedical_Device_PCB/Documentation/Notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11D2717-301D-754C-B74E-B9DA2A71E1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E8E589-4709-C949-AA95-43ACB225555D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" tabRatio="683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34400" yWindow="680" windowWidth="29040" windowHeight="15720" tabRatio="683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -241,7 +241,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,6 +296,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="32">
     <border>
@@ -672,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -733,9 +739,6 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -802,9 +805,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -820,12 +820,6 @@
     <xf numFmtId="164" fontId="3" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -835,6 +829,7 @@
     <xf numFmtId="164" fontId="3" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -868,7 +863,24 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1262,7 +1274,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="49" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -1270,10 +1282,10 @@
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="51" t="s">
         <v>38</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -1285,22 +1297,22 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I3" s="49"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="52" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="2"/>
@@ -1308,7 +1320,7 @@
     </row>
     <row r="5" spans="1:10" ht="36.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="24"/>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="37" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="26"/>
@@ -1317,118 +1329,118 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="74" t="s">
+      <c r="I5" s="71" t="s">
         <v>8</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46">
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45">
         <v>46143</v>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="45">
         <v>44681</v>
       </c>
-      <c r="I6" s="74"/>
+      <c r="I6" s="71"/>
     </row>
     <row r="7" spans="1:10" ht="25.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="45">
         <v>46146</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="45">
         <v>46147</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="45">
         <v>46148</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="45">
         <v>46149</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="45">
         <v>46150</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="49" t="s">
+      <c r="I7" s="48" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="45">
         <v>46153</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="45">
         <v>46154</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="45">
         <v>46155</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="45">
         <v>46156</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="45">
         <v>46157</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="7"/>
     </row>
     <row r="9" spans="1:10" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="72">
         <v>46160</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="72">
         <v>46161</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="72">
         <v>46162</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="72">
         <v>46163</v>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="72">
         <v>46164</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="73">
         <v>46167</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="72">
         <v>46168</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="72">
         <v>46169</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="72">
         <v>46170</v>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="72">
         <v>46171</v>
       </c>
       <c r="H10" s="3"/>
@@ -1437,84 +1449,84 @@
     <row r="11" spans="1:10" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="28"/>
       <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="75"/>
       <c r="H11" s="3"/>
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="B12" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="72">
         <v>46174</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="72">
         <v>46175</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="72">
         <v>46176</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="72">
         <v>46177</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G12" s="76">
         <v>46178</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="72">
         <v>46181</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="72">
         <v>46182</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="72">
         <v>46183</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="72">
         <v>46184</v>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="72">
         <v>46185</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="42">
         <v>44723</v>
       </c>
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="25"/>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="72">
         <v>46188</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="72">
         <v>46189</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="72">
         <v>46190</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="72">
         <v>46191</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="72">
         <v>46192</v>
       </c>
       <c r="H14" s="3"/>
@@ -1522,22 +1534,22 @@
     </row>
     <row r="15" spans="1:10" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="25"/>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="72">
         <v>46195</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="72">
         <v>46196</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="72">
         <v>46197</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="72">
         <v>46198</v>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="72">
         <v>46199</v>
       </c>
       <c r="H15" s="3"/>
@@ -1545,50 +1557,50 @@
     </row>
     <row r="16" spans="1:10" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="25"/>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="77">
         <v>46202</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="77">
         <v>46203</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
       <c r="H16" s="19"/>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="27"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="58"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
       <c r="H17" s="3"/>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="62">
+      <c r="C18" s="57"/>
+      <c r="D18" s="58">
         <v>45839</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="72">
         <v>46204</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="72">
         <v>46205</v>
       </c>
-      <c r="G18" s="59">
+      <c r="G18" s="73">
         <v>46206</v>
       </c>
       <c r="H18" s="19"/>
@@ -1598,124 +1610,124 @@
       <c r="A19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="72">
         <v>46209</v>
       </c>
-      <c r="D19" s="43">
+      <c r="D19" s="72">
         <v>46210</v>
       </c>
-      <c r="E19" s="43">
+      <c r="E19" s="72">
         <v>46211</v>
       </c>
-      <c r="F19" s="43">
+      <c r="F19" s="72">
         <v>46212</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="72">
         <v>46213</v>
       </c>
-      <c r="H19" s="43">
+      <c r="H19" s="42">
         <v>46214</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="72">
         <v>46216</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="72">
         <v>46217</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="72">
         <v>46218</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="72">
         <v>46219</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="72">
         <v>46220</v>
       </c>
-      <c r="H20" s="43">
+      <c r="H20" s="42">
         <v>46221</v>
       </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="72">
         <v>46223</v>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="72">
         <v>46224</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="72">
         <v>46225</v>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="72">
         <v>46226</v>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="72">
         <v>46227</v>
       </c>
-      <c r="H21" s="43">
+      <c r="H21" s="42">
         <v>46228</v>
       </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="72">
         <v>46230</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="72">
         <v>46231</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="72">
         <v>46232</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="72">
         <v>46233</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="72">
         <v>46234</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="36"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:9" ht="25.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="43">
+      <c r="C24" s="54"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="42">
         <v>44779</v>
       </c>
       <c r="I24" s="1"/>
@@ -1724,22 +1736,22 @@
       <c r="A25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="72">
         <v>46237</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="72">
         <v>46238</v>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="72">
         <v>46239</v>
       </c>
-      <c r="F25" s="43">
+      <c r="F25" s="72">
         <v>46240</v>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="72">
         <v>46241</v>
       </c>
       <c r="H25" s="3"/>
@@ -1747,29 +1759,29 @@
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="72">
         <v>46244</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="72">
         <v>45881</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="72">
         <v>45882</v>
       </c>
-      <c r="F26" s="43">
+      <c r="F26" s="72">
         <v>45883</v>
       </c>
-      <c r="G26" s="43">
+      <c r="G26" s="72">
         <v>45884</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" ht="25.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="41" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="10">
@@ -1792,7 +1804,7 @@
     </row>
     <row r="28" spans="1:9" ht="25.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="22"/>
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="47" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="23">
@@ -1824,65 +1836,65 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:9" ht="14" x14ac:dyDescent="0.15">
-      <c r="A30" s="64" t="s">
+      <c r="A30" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="66"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="67"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="64"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A32" s="68" t="s">
+      <c r="A32" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="70"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="67"/>
     </row>
     <row r="33" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
-      <c r="H33" s="69"/>
-      <c r="I33" s="70"/>
+      <c r="A33" s="65"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="67"/>
     </row>
     <row r="34" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="71"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="73"/>
+      <c r="A34" s="68"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="70"/>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="11" t="s">
@@ -1951,7 +1963,7 @@
         <v>32</v>
       </c>
       <c r="H39" s="14"/>
-      <c r="I39" s="75">
+      <c r="I39" s="60">
         <v>46154</v>
       </c>
     </row>
